--- a/Data Extraction/verification/model_output_verif_worklist.xlsx
+++ b/Data Extraction/verification/model_output_verif_worklist.xlsx
@@ -2,157 +2,36 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="verification" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'verification'!$A$1:$M$101</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="2">
     <font>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
       <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color rgb="FF9C5700"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -161,179 +40,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.7999816888943144"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.5999938962981048"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.3999755851924192"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.3999755851924192"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.7999816888943144"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.5999938962981048"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.3999755851924192"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7999816888943144"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.5999938962981048"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.3999755851924192"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.7999816888943144"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.5999938962981048"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.3999755851924192"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7999816888943144"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.5999938962981048"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.3999755851924192"/>
-        <bgColor indexed="65"/>
+        <fgColor rgb="00DDE5F0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -341,221 +52,23 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.3999755851924192"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="42">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Title" xfId="1" builtinId="15"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19"/>
-    <cellStyle name="Good" xfId="6" builtinId="26"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28"/>
-    <cellStyle name="Input" xfId="9" builtinId="20"/>
-    <cellStyle name="Output" xfId="10" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11"/>
-    <cellStyle name="Note" xfId="15" builtinId="10"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53"/>
-    <cellStyle name="Total" xfId="17" builtinId="25"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -638,44 +151,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -702,32 +215,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -754,24 +249,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -783,162 +260,166 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -949,5386 +430,5582 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M101"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8.578125" customWidth="1" min="1" max="1"/>
-    <col width="10.578125" customWidth="1" min="2" max="2"/>
-    <col width="28.578125" customWidth="1" min="3" max="3"/>
-    <col width="13.578125" customWidth="1" min="4" max="4"/>
-    <col width="45.578125" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" style="1" min="6" max="6"/>
-    <col width="48" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="80.3671875" customWidth="1" style="1" min="8" max="8"/>
-    <col width="49.9453125" customWidth="1" style="1" min="9" max="9"/>
-    <col width="54.9453125" customWidth="1" style="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="60" bestFit="1" customWidth="1" min="12" max="12"/>
-    <col width="28" bestFit="1" customWidth="1" min="13" max="13"/>
-    <col width="26.9453125" customWidth="1" min="14" max="14"/>
-    <col width="32.3125" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Fund</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Table</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Table contents</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Issue</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Model cited</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Page</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Folder</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Correct source</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>1-HIGH</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>aus_ff</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Austin (TX) Fire</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>the table's OWN printed totals do not add up from its cells | headcount disagrees with an independent database</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>TX_AUSTINCITY-COAFFRP_AV_2017_216.pdf</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>p21 AGE AND SERVICE DISTRIBUTION</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>p21</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/aus_ff_Age_Serv_Num_20260729_133657</t>
         </is>
       </c>
-      <c r="K2" s="4" t="n"/>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>1-HIGH</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>aus_pol</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Austin (TX) Police</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Retirement</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Retirees: count and average benefit by age band</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>output audit: SUSPECT:counts-fractional</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>TX_AUSTINCITY-COAPRS_AV_2019_217.pdf</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>p48 Annuitants – Distribution by Age and Cat</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>p48</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/aus_pol_Retirement_20260729_140517</t>
         </is>
       </c>
-      <c r="K3" s="4" t="n"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>1-HIGH</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>chi_pol</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Chicago (IL) Police</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Age_Serv_Wage</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Active members: average salary by age x years of service</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>the table's OWN printed totals do not add up from its cells</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>IL_CHICAGOCITY-PABF_AV_2019_146.pdf</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>p46 Exhibit C – Part III Total Lives and Ann; p46 Exhibit C – Part III Total Lives and Ann</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>p46</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/chi_pol_Age_Serv_Wage_20260729_152248</t>
         </is>
       </c>
-      <c r="K4" s="4" t="n"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>1-HIGH</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>dal</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Dallas (TX) ERS</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Avg_Mort</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Mortality (death) probability by age</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>output audit: SUSPECT:constant-column, SUSPECT:mortality-level</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Tx_Dallas_ERF_AV_2019_201.pdf</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>p50 Disability Mortality Rate; p50 Mortality Rate (Other Benefit Recipients; p51 Mortality Rate (Active Members)</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>p53  (the model cited p50 - it used the PRINTED page number; the table is on p53 of the PDF)</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/dal_Avg_Mort_20260729_160533</t>
         </is>
       </c>
-      <c r="K5" s="4" t="n"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>1-HIGH</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>dal_pf</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Dallas (TX) Police and Fire</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>the table's OWN printed totals do not add up from its cells | headcount disagrees with an independent database</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>TX_DALLASCITY-DPFP_AV_2019_153.pdf</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>p38 Exhibit B-1: Total Members in Active Ser</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>p38</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/dal_pf_Age_Serv_Num_20260729_160706</t>
         </is>
       </c>
-      <c r="K6" s="4" t="n"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>1-HIGH</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>dal_pf</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Dallas (TX) Police and Fire</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Age_Serv_Wage</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Active members: average salary by age x years of service</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>the table's OWN printed totals do not add up from its cells</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>TX_DALLASCITY-DPFP_AV_2019_153.pdf</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>p38 Exhibit B-1: Total Members in Active Ser; p38 Exhibit B-1: Total Members in Active Ser</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>p38</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/dal_pf_Age_Serv_Wage_20260729_161651</t>
         </is>
       </c>
-      <c r="K7" s="4" t="n"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>1-HIGH</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>dc_pf</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>DC Police &amp; Fire</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>headcount disagrees with an independent database</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>DC_DCRB-PFRS-TRS_AV_2019_19_20.pdf</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>p33 Active Age/Service Distribution Includin; p34 Active Age/Service Distribution Includin; p35 Active Age/Service Distribution Includin</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>p33</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/dc_pf_Age_Serv_Num_20260729_163957</t>
         </is>
       </c>
-      <c r="K8" s="4" t="n"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>1-HIGH</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>dc_teach</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>DC Teachers</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>headcount disagrees with an independent database</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>DC_DCRB-PFRS-TRS_AV_2019_19_20.pdf</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>p33 Active Age/Service Distribution Includin; p34 Active Age/Service Distribution Includin; p35 Active Age/Service Distribution Includin</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>p33</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/dc_teach_Age_Serv_Num_20260729_171405</t>
         </is>
       </c>
-      <c r="K9" s="4" t="n"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>1-HIGH</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>den_schools</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Denver (CO) Schools</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>headcount disagrees with an independent database</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>CO_CO-PERA-LGD-SCDTF-SDTF_AV_2019_13_14_15_23.pdf</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>p115 Exhibit C: Schedule of Active Member Dat; p116 Exhibit C: Schedule of Active Member Dat; p117 Exhibit C: Schedule of Active Member Dat</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>p115</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/den_schools_Age_Serv_Num_20260729_175326</t>
         </is>
       </c>
-      <c r="K10" s="4" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>1-HIGH</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>den_schools</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Denver (CO) Schools</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Age_Serv_Wage</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Active members: average salary by age x years of service</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>the table's OWN printed totals do not add up from its cells | output audit: NOTE:sparse</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>CO_CO-PERA-LGD-SCDTF-SDTF_AV_2019_13_14_15_23.pdf</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>p115 Exhibit C: Schedule of Active Member Dat; p115 Exhibit C: Schedule of Active Member Dat; p116 Exhibit C: Schedule of Active Member Dat</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>p115</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/den_schools_Age_Serv_Wage_20260729_180002</t>
         </is>
       </c>
-      <c r="K11" s="4" t="n"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>1-HIGH</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>hou_ff</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Houston (TX) Firefighters</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>the table's OWN printed totals do not add up from its cells | headcount disagrees with an independent database</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>TX_HOUSTONCITY-HFRRF_AV_2020_30.pdf</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>p18 Summary of Active Participants as of Jul</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>p18  (only some values located automatically - check carefully)</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/hou_ff_Age_Serv_Num_20260729_183229</t>
         </is>
       </c>
-      <c r="K12" s="4" t="n"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>1-HIGH</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>hou_ff</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Houston (TX) Firefighters</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Age_Serv_Wage</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Active members: average salary by age x years of service</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>the table's OWN printed totals do not add up from its cells</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>TX_HOUSTONCITY-HFRRF_AV_2020_30.pdf</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>p18 Summary of Active Participants as of Jul; p18 Summary of Active Participants as of Jul</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>p18</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/hou_ff_Age_Serv_Wage_20260729_184013</t>
         </is>
       </c>
-      <c r="K13" s="4" t="n"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>1-HIGH</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>hou_gen</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Houston (TX) Municipal</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Age_Serv_Wage</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Active members: average salary by age x years of service</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>the table's OWN printed totals do not add up from its cells</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>TX_HMERF_AV_2019_204.pdf</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>p48 Distribution of All Active Members by Ag; p48 Distribution of All Active Members by Ag</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>p48</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/hou_gen_Age_Serv_Wage_20260729_184748</t>
         </is>
       </c>
-      <c r="K14" s="4" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>1-HIGH</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>hou_pol</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Houston (TX) Police</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>the table's OWN printed totals do not add up from its cells</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>TX_HOUSTONCITY-HPOPS_AV_2019_208.pdf</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>p47 DISTRIBUTION OF ACTIVE MEMBERS BY AGE AN; p48 DISTRIBUTION OF ACTIVE MEMBERS BY AGE AN; p49 DISTRIBUTION OF ACTIVE MEMBERS BY AGE AN</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>p41  (the model cited p47 - it used the PRINTED page number; the table is on p41 of the PDF)</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/hou_pol_Age_Serv_Num_20260729_191648</t>
         </is>
       </c>
-      <c r="K15" s="4" t="n"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>1-HIGH</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>lax_uty</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Los Angeles (CA) Water and Power</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>the table's OWN printed totals do not add up from its cells</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>CA_LACITY-DWP_AV_2019_141.pdf</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>p45 EXHIBIT B – MEMBERS IN ACTIVE SERVICE AS</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>p45</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/lax_uty_Age_Serv_Num_20260729_200248</t>
         </is>
       </c>
-      <c r="K16" s="4" t="n"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>1-HIGH</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>lax_uty</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Los Angeles (CA) Water and Power</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Age_Serv_Wage</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Active members: average salary by age x years of service</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>the table's OWN printed totals do not add up from its cells</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>CA_LACITY-DWP_AV_2019_141.pdf</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>p45 EXHIBIT B – MEMBERS IN ACTIVE SERVICE AS; p45 EXHIBIT B – MEMBERS IN ACTIVE SERVICE AS</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>p45</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/lax_uty_Age_Serv_Wage_20260729_201100</t>
         </is>
       </c>
-      <c r="K17" s="4" t="n"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>1-HIGH</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>nyc_ers</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>New York City (NY) ERS</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>the table's OWN printed totals do not add up from its cells</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>NY_NYC-ERS_AV_2020_76.pdf</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t xml:space="preserve">p99 Detailed Active Membership and Salaries ; p100 Detailed Active Membership and Salaries ; p101 Detailed Active Membership and Salaries </t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>p99</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/nyc_ers_Age_Serv_Num_20260729_213712</t>
         </is>
       </c>
-      <c r="K18" s="4" t="n"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>1-HIGH</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>nyc_pol</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>New York City (NY) Police</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>the table's OWN printed totals do not add up from its cells</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>NY_NYC-PPF_AV_2020_150.pdf</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t xml:space="preserve">p78 Detailed Active Membership and Salaries </t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>p80  (the model cited p78 - it used the PRINTED page number; the table is on p80 of the PDF)</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/nyc_pol_Age_Serv_Num_20260729_222248</t>
         </is>
       </c>
-      <c r="K19" s="4" t="n"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>1-HIGH</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>sea</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Seattle (WA) ERS</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>the table's OWN printed totals do not add up from its cells</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>WA_SEATTLECITY-ERS_AV_2019_156.pdf</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>p63 Distribution of Employees and Salaries a</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>p63</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/sea_Age_Serv_Num_20260729_234956</t>
         </is>
       </c>
-      <c r="K20" s="4" t="n"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>aus</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Austin (TX) ERS</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>TX_AUSTINCITY-COAERS_AV_2019_12.pdf</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t xml:space="preserve">p36 Distribution of All Active Participants </t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>p36</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/aus_Age_Serv_Num_20260729_132148</t>
         </is>
       </c>
-      <c r="K21" s="4" t="n"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>aus</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Austin (TX) ERS</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Age_Serv_Wage</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Active members: average salary by age x years of service</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>TX_AUSTINCITY-COAERS_AV_2019_12.pdf</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t xml:space="preserve">p36 Distribution of All Active Participants ; p36 Distribution of All Active Participants </t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>p36</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/aus_Age_Serv_Wage_20260729_132217</t>
         </is>
       </c>
-      <c r="K22" s="4" t="n"/>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>aus</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Austin (TX) ERS</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Avg_Mort</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Mortality (death) probability by age</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>TX_AUSTINCITY-COAERS_AV_2019_12.pdf</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>p49 Rates of Decrement Due to Disability; p36 Distribution of All Active Participants ; p31 Schedule of Retirees and Beneficiaries A</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>p49</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/aus_Avg_Mort_20260729_133456</t>
         </is>
       </c>
-      <c r="K23" s="4" t="n"/>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>aus_pol</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Austin (TX) Police</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>TX_AUSTINCITY-COAPRS_AV_2019_217.pdf</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>p47 Table D Active Members – Distribution by</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>p47  (only some values located automatically - check carefully)</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/aus_pol_Age_Serv_Num_20260729_134401</t>
         </is>
       </c>
-      <c r="K24" s="4" t="n"/>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>aus_pol</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Austin (TX) Police</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Age_Serv_Wage</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Active members: average salary by age x years of service</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>TX_AUSTINCITY-COAPRS_AV_2019_217.pdf</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>p47 Active Members – Distribution by Age and; p47 Active Members – Distribution by Age and</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>p47</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/aus_pol_Age_Serv_Wage_20260729_134452</t>
         </is>
       </c>
-      <c r="K25" s="4" t="n"/>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>aus_pol</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Austin (TX) Police</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Sep_Rate</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Termination/withdrawal rates by age x service</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>TX_AUSTINCITY-COAPRS_AV_2019_217.pdf</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>p39 Termination Decrements for Reasons Other</t>
         </is>
       </c>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/aus_pol_Sep_Rate_20260729_134737</t>
         </is>
       </c>
-      <c r="K26" s="4" t="n"/>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>bos</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Boston (MA) RS</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>MA_BOSTONCITY-SBRS_AV_2019_148.pdf</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>p49 Exhibit A: Participants in Active Servic; p51 Exhibit C: Participants in Active Servic</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>p49</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/bos_Age_Serv_Num_20260729_140542</t>
         </is>
       </c>
-      <c r="K27" s="4" t="n"/>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>bos</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Boston (MA) RS</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Age_Serv_Wage</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Active members: average salary by age x years of service</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>MA_BOSTONCITY-SBRS_AV_2019_148.pdf</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>p49 Exhibit A: Participants in Active Servic; p49 Exhibit A: Participants in Active Servic</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>p49</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/bos_Age_Serv_Wage_20260729_140626</t>
         </is>
       </c>
-      <c r="K28" s="4" t="n"/>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>bos</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Boston (MA) RS</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Avg_Mort</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Mortality (death) probability by age</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>MA_BOSTONCITY-SBRS_AV_2019_148.pdf</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>p64 Termination Rates before Retirement: Gro; p65 Group 4 Rate (%) – BRS excluding Teacher; p66 Rate (%) – Teachers</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>p64</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/bos_Avg_Mort_20260729_141632</t>
         </is>
       </c>
-      <c r="K29" s="4" t="n"/>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>clt_ff</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Charlotte (NC) Firefighters' RS</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Sep_Rate</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Termination/withdrawal rates by age x service</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>NC_CHARLOTTE-FRS_AV_2022_182.pdf</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>p21 Annual Rate of Separation from Active Se</t>
         </is>
       </c>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/clt_ff_Sep_Rate_20260729_160134</t>
         </is>
       </c>
-      <c r="K30" s="4" t="n"/>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>dc_pf</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>DC Police &amp; Fire</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Age_Serv_Wage</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Active members: average salary by age x years of service</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>DC_DCRB-PFRS-TRS_AV_2019_19_20.pdf</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>p33 Active Age/Service Distribution Includin; p33 Active Age/Service Distribution Includin; p34 Active Age/Service Distribution Includin</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>p33</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/dc_pf_Age_Serv_Wage_20260729_164259</t>
         </is>
       </c>
-      <c r="K31" s="4" t="n"/>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>dc_pf</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>DC Police &amp; Fire</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Retirement</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Retirees: count and average benefit by age band</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>DC_DCRB-PFRS-TRS_AV_2019_19_20.pdf</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>p39 Schedule of Retiree Member Data – Teache; p42 Schedule of Retiree Member Data – Police; p45 Schedule of Retiree Member Data – Fire –</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>p39</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/dc_pf_Retirement_20260729_170600</t>
         </is>
       </c>
-      <c r="K32" s="4" t="n"/>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>dc_teach</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>DC Teachers</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Age_Serv_Wage</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Active members: average salary by age x years of service</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>DC_DCRB-PFRS-TRS_AV_2019_19_20.pdf</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>p33 Active Age/Service Distribution Includin; p33 Active Age/Service Distribution Includin; p34 Active Age/Service Distribution Includin</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>p33</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/dc_teach_Age_Serv_Wage_20260729_171708</t>
         </is>
       </c>
-      <c r="K33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>dc_teach</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>DC Teachers</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Retirement</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Retirees: count and average benefit by age band</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>DC_DCRB-PFRS-TRS_AV_2019_19_20.pdf</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>p39 Schedule of Retiree Member Data – Teache; p42 Schedule of Retiree Member Data – Police; p45 Schedule of Retiree Member Data – Fire –</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>p39</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/dc_teach_Retirement_20260729_174008</t>
         </is>
       </c>
-      <c r="K34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>den</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Denver (CO) Employees</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>CO_DENVERCITYCOUNTY-DERP_AV_2019_22.pdf</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t xml:space="preserve">p57 Age and Service Distribution for Active </t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>p57</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/den_Age_Serv_Num_20260729_174814</t>
         </is>
       </c>
-      <c r="K35" s="4" t="n"/>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>den_schools</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Denver (CO) Schools</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Avg_Mort</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Mortality (death) probability by age</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>CO_CO-PERA-LGD-SCDTF-SDTF_AV_2019_13_14_15_23.pdf</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t xml:space="preserve">p145 Single Life Retirement Values and Rates ; p145 Single Life Retirement Values and Rates ; p146 Single Life Retirement Values and Rates </t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>p145</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/den_schools_Avg_Mort_20260729_182840</t>
         </is>
       </c>
-      <c r="K36" s="4" t="n"/>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>lax_ffpol</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Los Angeles (CA) Fire and Police</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Avg_Mort</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Mortality (death) probability by age</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>CA_LACITY-LAFPP_AV_2019_140.pdf</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>p92 Pre-Retirement Mortality Rates; p91 Post-Retirement Mortality Rates - Health; p91 Post-Retirement Mortality Rates - Disabl</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>p81  (the model cited p92 - it used the PRINTED page number; the table is on p81 of the PDF)</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/lax_ffpol_Avg_Mort_20260729_192959</t>
         </is>
       </c>
-      <c r="K37" s="4" t="n"/>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>lax_gen</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Los Angeles (CA) ERS</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Avg_Mort</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Mortality (death) probability by age</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>CA_LACITY-LACERS_AV_2019_139.pdf</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>p69 Pre-Retirement Mortality Rates; p68 Post-Retirement Mortality Rates - Health; p68 Post-Retirement Mortality Rates - Disabl</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>p58  (the model cited p69 - it used the PRINTED page number; the table is on p58 of the PDF)</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/lax_gen_Avg_Mort_20260729_200106</t>
         </is>
       </c>
-      <c r="K38" s="4" t="n"/>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>lax_uty</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Los Angeles (CA) Water and Power</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Avg_Mort</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Mortality (death) probability by age</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>CA_LACITY-DWP_AV_2019_141.pdf</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>p62 Pre-Retirement Mortality Rates; p61 Post-Retirement Mortality Rates; p45 Distribution of Active Participants as o</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>p62</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/lax_uty_Avg_Mort_20260729_201548</t>
         </is>
       </c>
-      <c r="K39" s="4" t="n"/>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>nyc_edu</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>New York City (NY) Educational</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>NY_NYC-BERS_AV_2018_211.pdf</t>
         </is>
       </c>
-      <c r="H40" s="5" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t xml:space="preserve">p70 Detailed Active Membership and Salaries </t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>p72  (the model cited p70 - it used the PRINTED page number; the table is on p72 of the PDF)</t>
         </is>
       </c>
-      <c r="J40" s="5" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/nyc_edu_Age_Serv_Num_20260729_205502</t>
         </is>
       </c>
-      <c r="K40" s="4" t="n"/>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>nyc_edu</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>New York City (NY) Educational</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Age_Serv_Wage</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Active members: average salary by age x years of service</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>NY_NYC-BERS_AV_2018_211.pdf</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t xml:space="preserve">p70 Detailed Active Membership and Salaries ; p70 Detailed Active Membership and Salaries </t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>p72  (the model cited p70 - it used the PRINTED page number; the table is on p72 of the PDF)</t>
         </is>
       </c>
-      <c r="J41" s="5" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/nyc_edu_Age_Serv_Wage_20260729_205618</t>
         </is>
       </c>
-      <c r="K41" s="4" t="n"/>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>nyc_edu</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>New York City (NY) Educational</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Retirement</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Retirees: count and average benefit by age band</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>NY_NYC-BERS_AV_2018_211.pdf</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>p76 Distribution of Pension Benefits by Caus</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>p76</t>
         </is>
       </c>
-      <c r="J42" s="5" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/nyc_edu_Retirement_20260729_213644</t>
         </is>
       </c>
-      <c r="K42" s="4" t="n"/>
-    </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>nyc_edu</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>New York City (NY) Educational</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Sep_Rate</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Termination/withdrawal rates by age x service</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
         <is>
           <t>NY_NYC-BERS_AV_2018_211.pdf</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>p54 Table XI-2 Active Termination Rates</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>p54</t>
         </is>
       </c>
-      <c r="J43" s="5" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/nyc_edu_Sep_Rate_20260729_212713</t>
         </is>
       </c>
-      <c r="K43" s="4" t="n"/>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>nyc_pol</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>New York City (NY) Police</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Age_Serv_Wage</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Active members: average salary by age x years of service</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>NY_NYC-PPF_AV_2020_150.pdf</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t xml:space="preserve">p74 Detailed Active Membership and Salaries ; p74 Detailed Active Membership and Salaries </t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>p80  (the model cited p74 - it used the PRINTED page number; the table is on p80 of the PDF)</t>
         </is>
       </c>
-      <c r="J44" s="5" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/nyc_pol_Age_Serv_Wage_20260729_222517</t>
         </is>
       </c>
-      <c r="K44" s="4" t="n"/>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>2-MED</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>nyc_pol</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>New York City (NY) Police</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Retirement</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Retirees: count and average benefit by age band</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
         <is>
           <t>NY_NYC-PPF_AV_2020_150.pdf</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>p84 Distribution of Pension Benefits by Caus</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>p84</t>
         </is>
       </c>
-      <c r="J45" s="5" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/nyc_pol_Retirement_20260729_230954</t>
         </is>
       </c>
-      <c r="K45" s="4" t="n"/>
-    </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>chi_edu</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Chicago (IL) Teachers</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
         <is>
           <t>IL_CHICAGOCITY-CTPF_AV_2019_11.pdf</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>p55 Table 13 — Total Lives and Annual Salari</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>p55</t>
         </is>
       </c>
-      <c r="J46" s="5" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/chi_edu_Age_Serv_Num_20260729_141740</t>
         </is>
       </c>
-      <c r="K46" s="4" t="n"/>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>chi_edu</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Chicago (IL) Teachers</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Ret_Rate</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Retirement rates by age x service</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
         <is>
           <t>IL_CHICAGOCITY-CTPF_AV_2019_11.pdf</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>p66 Retirement Rates for Tier 1 Employees an</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>p66</t>
         </is>
       </c>
-      <c r="J47" s="5" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/chi_edu_Ret_Rate_20260729_141836</t>
         </is>
       </c>
-      <c r="K47" s="4" t="n"/>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>chi_edu</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Chicago (IL) Teachers</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Sep_Rate</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Termination/withdrawal rates by age x service</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
         <is>
           <t>IL_CHICAGOCITY-CTPF_AV_2019_11.pdf</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>p64 Termination Rates by Service</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>p58  (the model cited p64 - it used the PRINTED page number; the table is on p58 of the PDF)</t>
         </is>
       </c>
-      <c r="J48" s="5" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/chi_edu_Sep_Rate_20260729_141915</t>
         </is>
       </c>
-      <c r="K48" s="4" t="n"/>
-    </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>chi_ff</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Chicago (IL) Fire</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
         <is>
           <t>IL_CHICAGOCITY-FABF_AV_2019_206.pdf</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>p32 Exhibit B.1 – All Members in Active Serv</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>p32</t>
         </is>
       </c>
-      <c r="J49" s="5" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/chi_ff_Age_Serv_Num_20260729_142254</t>
         </is>
       </c>
-      <c r="K49" s="4" t="n"/>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>chi_ff</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Chicago (IL) Fire</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Retirement</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Retirees: count and average benefit by age band</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
         <is>
           <t>IL_CHICAGOCITY-FABF_AV_2019_206.pdf</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>p37 Exhibit D.1 – Service Retirement Annuita</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>p37</t>
         </is>
       </c>
-      <c r="J50" s="5" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/chi_ff_Retirement_20260729_145740</t>
         </is>
       </c>
-      <c r="K50" s="4" t="n"/>
-    </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>chi_ff</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Chicago (IL) Fire</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Sep_Rate</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Termination/withdrawal rates by age x service</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G51" s="4" t="inlineStr">
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
         <is>
           <t>IL_CHICAGOCITY-FABF_AV_2019_206.pdf</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>p69 Termination Rates</t>
         </is>
       </c>
-      <c r="I51" s="5" t="n"/>
-      <c r="J51" s="5" t="inlineStr">
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/chi_ff_Sep_Rate_20260729_144450</t>
         </is>
       </c>
-      <c r="K51" s="4" t="n"/>
-    </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>chi_gen</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Chicago (IL) Municipal</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="inlineStr">
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
         <is>
           <t>IL_CHICAGOCITY-MEABF_AV_2019_145.pdf</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>p32 Exhibit B.1 All Members in Active Servic</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>p32</t>
         </is>
       </c>
-      <c r="J52" s="5" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/chi_gen_Age_Serv_Num_20260729_145812</t>
         </is>
       </c>
-      <c r="K52" s="4" t="n"/>
-    </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>chi_gen</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Chicago (IL) Municipal</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Retirement</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Retirees: count and average benefit by age band</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G53" s="4" t="inlineStr">
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
         <is>
           <t>IL_CHICAGOCITY-MEABF_AV_2019_145.pdf</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>p38 Employee Annuitants as of December 31, 2</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>p38</t>
         </is>
       </c>
-      <c r="J53" s="5" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/chi_gen_Retirement_20260729_152131</t>
         </is>
       </c>
-      <c r="K53" s="4" t="n"/>
-    </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>chi_gen</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Chicago (IL) Municipal</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Sep_Rate</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Termination/withdrawal rates by age x service</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
         <is>
           <t>IL_CHICAGOCITY-MEABF_AV_2019_145.pdf</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>p71 Termination Rates</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>p62  (the model cited p71 - it used the PRINTED page number; the table is on p62 of the PDF)</t>
         </is>
       </c>
-      <c r="J54" s="5" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/chi_gen_Sep_Rate_20260729_151333</t>
         </is>
       </c>
-      <c r="K54" s="4" t="n"/>
-    </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>chi_pol</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Chicago (IL) Police</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Retirement</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Retirees: count and average benefit by age band</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>IL_CHICAGOCITY-PABF_AV_2019_146.pdf</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>p38 Exhibit E - Showing Statistics on Servic</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>p49  (the model cited p38 - it used the PRINTED page number; the table is on p49 of the PDF)</t>
         </is>
       </c>
-      <c r="J55" s="5" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/chi_pol_Retirement_20260729_155245</t>
         </is>
       </c>
-      <c r="K55" s="4" t="n"/>
-    </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>chi_pol</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Chicago (IL) Police</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Sep_Rate</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Termination/withdrawal rates by age x service</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
         <is>
           <t>IL_CHICAGOCITY-PABF_AV_2019_146.pdf</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>p72 Rate of Termination</t>
         </is>
       </c>
-      <c r="I56" s="5" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>p72</t>
         </is>
       </c>
-      <c r="J56" s="5" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/chi_pol_Sep_Rate_20260729_155012</t>
         </is>
       </c>
-      <c r="K56" s="4" t="n"/>
-    </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>dal</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Dallas (TX) ERS</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="inlineStr">
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
         <is>
           <t>Tx_Dallas_ERF_AV_2019_201.pdf</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>p37 Distribution of Active Members and Payro</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>p37</t>
         </is>
       </c>
-      <c r="J57" s="5" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/dal_Age_Serv_Num_20260729_160327</t>
         </is>
       </c>
-      <c r="K57" s="4" t="n"/>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>dal</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Dallas (TX) ERS</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Age_Serv_Wage</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Active members: average salary by age x years of service</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
         <is>
           <t>Tx_Dallas_ERF_AV_2019_201.pdf</t>
         </is>
       </c>
-      <c r="H58" s="5" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>p37 Distribution of Active Members and Payro; p37 Distribution of Active Members and Payro</t>
         </is>
       </c>
-      <c r="I58" s="5" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>p37</t>
         </is>
       </c>
-      <c r="J58" s="5" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/dal_Age_Serv_Wage_20260729_160345</t>
         </is>
       </c>
-      <c r="K58" s="4" t="n"/>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>dal</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Dallas (TX) ERS</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Retirement</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Retirees: count and average benefit by age band</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
         <is>
           <t>Tx_Dallas_ERF_AV_2019_201.pdf</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>p38 Distribution of Benefit Recipients</t>
         </is>
       </c>
-      <c r="I59" s="5" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>p38</t>
         </is>
       </c>
-      <c r="J59" s="5" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/dal_Retirement_20260729_160651</t>
         </is>
       </c>
-      <c r="K59" s="4" t="n"/>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>dal</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Dallas (TX) ERS</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>Sep_Rate</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>Termination/withdrawal rates by age x service</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
         <is>
           <t>Tx_Dallas_ERF_AV_2019_201.pdf</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>p54 General Turnover (Terminations per 1,000</t>
         </is>
       </c>
-      <c r="I60" s="5" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>p57  (the model cited p54 - it used the PRINTED page number; the table is on p57 of the PDF)</t>
         </is>
       </c>
-      <c r="J60" s="5" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/dal_Sep_Rate_20260729_160455</t>
         </is>
       </c>
-      <c r="K60" s="4" t="n"/>
-    </row>
-    <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>dal_pf</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Dallas (TX) Police and Fire</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Sep_Rate</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Termination/withdrawal rates by age x service</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
         <is>
           <t>TX_DALLASCITY-DPFP_AV_2019_153.pdf</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>p53 Withdrawal Rates Before Retirement</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>p53  (only some values located automatically - check carefully)</t>
         </is>
       </c>
-      <c r="J61" s="5" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/dal_pf_Sep_Rate_20260729_162714</t>
         </is>
       </c>
-      <c r="K61" s="4" t="n"/>
-    </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>den</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Denver (CO) Employees</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>Avg_Mort</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Mortality (death) probability by age</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
         <is>
           <t>CO_DENVERCITYCOUNTY-DERP_AV_2019_22.pdf</t>
         </is>
       </c>
-      <c r="H62" s="5" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t xml:space="preserve">p62 Rates of Mortality - Active Mortality Sa; p53 Age and Service Distribution for Active </t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>p63  (the model cited p62 - it used the PRINTED page number; the table is on p63 of the PDF)</t>
         </is>
       </c>
-      <c r="J62" s="5" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/den_Avg_Mort_20260729_175218</t>
         </is>
       </c>
-      <c r="K62" s="4" t="n"/>
-    </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>den</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Denver (CO) Employees</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>Sep_Rate</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Termination/withdrawal rates by age x service</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
         <is>
           <t>CO_DENVERCITYCOUNTY-DERP_AV_2019_22.pdf</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>p58 Rates of Termination</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>p50  (the model cited p58 - it used the PRINTED page number; the table is on p50 of the PDF)</t>
         </is>
       </c>
-      <c r="J63" s="5" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/den_Sep_Rate_20260729_175157</t>
         </is>
       </c>
-      <c r="K63" s="4" t="n"/>
-    </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>hou_gen</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Houston (TX) Municipal</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr">
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
         <is>
           <t>TX_HMERF_AV_2019_204.pdf</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>p48 Distribution of All Active Members by Ag</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>p48</t>
         </is>
       </c>
-      <c r="J64" s="5" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/hou_gen_Age_Serv_Num_20260729_184727</t>
         </is>
       </c>
-      <c r="K64" s="4" t="n"/>
-    </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>hou_pol</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Houston (TX) Police</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>Avg_Mort</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Mortality (death) probability by age</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
         <is>
           <t>TX_HOUSTONCITY-HPOPS_AV_2019_208.pdf</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>p55 Sample rates are shown below for 2019; p46 Distribution of Active Members by Age an; p46 Membership Data - Service Retirees</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>p55</t>
         </is>
       </c>
-      <c r="J65" s="5" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/hou_pol_Avg_Mort_20260729_192328</t>
         </is>
       </c>
-      <c r="K65" s="4" t="n"/>
-    </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>hou_pol</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Houston (TX) Police</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>Ret_Rate</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Retirement rates by age x service</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
         <is>
           <t>TX_HOUSTONCITY-HPOPS_AV_2019_208.pdf</t>
         </is>
       </c>
-      <c r="H66" s="5" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>p54 Retirement Rates</t>
         </is>
       </c>
-      <c r="I66" s="5" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>p54</t>
         </is>
       </c>
-      <c r="J66" s="5" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/hou_pol_Ret_Rate_20260729_192206</t>
         </is>
       </c>
-      <c r="K66" s="4" t="n"/>
-    </row>
-    <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>hou_pol</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Houston (TX) Police</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>Sep_Rate</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Termination/withdrawal rates by age x service</t>
         </is>
       </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
         <is>
           <t>TX_HOUSTONCITY-HPOPS_AV_2019_208.pdf</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>p56 Service Based Rates of Termination</t>
         </is>
       </c>
-      <c r="I67" s="5" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>p56</t>
         </is>
       </c>
-      <c r="J67" s="5" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/hou_pol_Sep_Rate_20260729_192254</t>
         </is>
       </c>
-      <c r="K67" s="4" t="n"/>
-    </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>lax_ffpol</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Los Angeles (CA) Fire and Police</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="inlineStr">
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
         <is>
           <t>CA_LACITY-LAFPP_AV_2019_140.pdf</t>
         </is>
       </c>
-      <c r="H68" s="5" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>p60 EXHIBIT B – MEMBERS IN ACTIVE SERVICE AS</t>
         </is>
       </c>
-      <c r="I68" s="5" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>p60</t>
         </is>
       </c>
-      <c r="J68" s="5" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/lax_ffpol_Age_Serv_Num_20260729_192439</t>
         </is>
       </c>
-      <c r="K68" s="4" t="n"/>
-    </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>lax_ffpol</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Los Angeles (CA) Fire and Police</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>Age_Serv_Wage</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>Active members: average salary by age x years of service</t>
         </is>
       </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
         <is>
           <t>CA_LACITY-LAFPP_AV_2019_140.pdf</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>p60 EXHIBIT B – MEMBERS IN ACTIVE SERVICE AS; p60 EXHIBIT B – MEMBERS IN ACTIVE SERVICE AS</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>p60</t>
         </is>
       </c>
-      <c r="J69" s="5" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/lax_ffpol_Age_Serv_Wage_20260729_192521</t>
         </is>
       </c>
-      <c r="K69" s="4" t="n"/>
-    </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>lax_gen</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Los Angeles (CA) ERS</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G70" s="4" t="inlineStr">
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
         <is>
           <t>CA_LACITY-LACERS_AV_2019_139.pdf</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>p53 EXHIBIT B – MEMBERS IN ACTIVE SERVICE AS</t>
         </is>
       </c>
-      <c r="I70" s="5" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>p53</t>
         </is>
       </c>
-      <c r="J70" s="5" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/lax_gen_Age_Serv_Num_20260729_193143</t>
         </is>
       </c>
-      <c r="K70" s="4" t="n"/>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>lax_gen</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Los Angeles (CA) ERS</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>Age_Serv_Wage</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>Active members: average salary by age x years of service</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G71" s="4" t="inlineStr">
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
         <is>
           <t>CA_LACITY-LACERS_AV_2019_139.pdf</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>p53 EXHIBIT B – MEMBERS IN ACTIVE SERVICE AS; p53 EXHIBIT B – MEMBERS IN ACTIVE SERVICE AS</t>
         </is>
       </c>
-      <c r="I71" s="5" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>p53</t>
         </is>
       </c>
-      <c r="J71" s="5" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/lax_gen_Age_Serv_Wage_20260729_193222</t>
         </is>
       </c>
-      <c r="K71" s="4" t="n"/>
-    </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>lax_uty</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Los Angeles (CA) Water and Power</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>Ret_Rate</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>Retirement rates by age x service</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G72" s="4" t="inlineStr">
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
         <is>
           <t>CA_LACITY-DWP_AV_2019_141.pdf</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>p64 Retirement Rates (%)</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>p64</t>
         </is>
       </c>
-      <c r="J72" s="5" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/lax_uty_Ret_Rate_20260729_201434</t>
         </is>
       </c>
-      <c r="K72" s="4" t="n"/>
-    </row>
-    <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>lax_uty</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Los Angeles (CA) Water and Power</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>Sep_Rate</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>Termination/withdrawal rates by age x service</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="inlineStr">
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
         <is>
           <t>CA_LACITY-DWP_AV_2019_141.pdf</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>p63 Termination Rates: Total Termination Rat</t>
         </is>
       </c>
-      <c r="I73" s="5" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>p74  (the model cited p63 - it used the PRINTED page number; the table is on p74 of the PDF)</t>
         </is>
       </c>
-      <c r="J73" s="5" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/lax_uty_Sep_Rate_20260729_201527</t>
         </is>
       </c>
-      <c r="K73" s="4" t="n"/>
-    </row>
-    <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>mil</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Milwaukee (WI) City ERS</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G74" s="4" t="inlineStr">
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>WI_MILWAUKEECITY-ERS_AV_2019_151.pdf</t>
         </is>
       </c>
-      <c r="H74" s="5" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>p72 DISTRIBUTION OF ACTIVE MEMBERS - General; p75 DISTRIBUTION OF ACTIVE MEMBERS - Policem; p76 DISTRIBUTION OF ACTIVE MEMBERS - Firemen</t>
         </is>
       </c>
-      <c r="I74" s="5" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>p72</t>
         </is>
       </c>
-      <c r="J74" s="5" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/mil_Age_Serv_Num_20260729_201652</t>
         </is>
       </c>
-      <c r="K74" s="4" t="n"/>
-    </row>
-    <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>mil</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Milwaukee (WI) City ERS</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>Retirement</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>Retirees: count and average benefit by age band</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
         <is>
           <t>WI_MILWAUKEECITY-ERS_AV_2019_151.pdf</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>p80 SUMMARY OF RETIRED MEMBERS - General Emp; p81 SUMMARY OF RETIRED MEMBERS - Policemen; p82 SUMMARY OF RETIRED MEMBERS - Firemen</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>p80</t>
         </is>
       </c>
-      <c r="J75" s="5" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/mil_Retirement_20260729_203437</t>
         </is>
       </c>
-      <c r="K75" s="4" t="n"/>
-    </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>mil</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Milwaukee (WI) City ERS</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>Sep_Rate</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>Termination/withdrawal rates by age x service</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G76" s="4" t="inlineStr">
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>WI_MILWAUKEECITY-ERS_AV_2019_151.pdf</t>
         </is>
       </c>
-      <c r="H76" s="5" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>p113 Illustrative Rates of Termination</t>
         </is>
       </c>
-      <c r="I76" s="5" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>p113</t>
         </is>
       </c>
-      <c r="J76" s="5" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/mil_Sep_Rate_20260729_202146</t>
         </is>
       </c>
-      <c r="K76" s="4" t="n"/>
-    </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>nsh</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Nashville-Davidson (TN) ERS</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G77" s="4" t="inlineStr">
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
         <is>
           <t>TN_NASHVILLECITY-MPP_AV_2019_158.pdf</t>
         </is>
       </c>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>p55 TABLE III-1 DISTRIBUTION OF SERVICE GROU; p56 TABLE III-2 DISTRIBUTION OF SERVICE GROU; p58 TABLE III-4 DISTRIBUTION OF SERVICE GROU</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>p43  (only some values located automatically - check carefully)</t>
         </is>
       </c>
-      <c r="J77" s="5" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/nsh_Age_Serv_Num_20260729_203655</t>
         </is>
       </c>
-      <c r="K77" s="4" t="n"/>
-    </row>
-    <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>nsh</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Nashville-Davidson (TN) ERS</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>Avg_Mort</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>Mortality (death) probability by age</t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G78" s="4" t="inlineStr">
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
         <is>
           <t>TN_NASHVILLECITY-MPP_AV_2019_158.pdf</t>
         </is>
       </c>
-      <c r="H78" s="5" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>p121 TABLE XIII - SUMMARY OF ACTUARIAL ASSUMP; p43 TABLE I-9 - DISTRIBUTION OF ACTIVE PARTI; p84 TABLE V-12 - DISTRIBUTION OF BASE BENEFI</t>
         </is>
       </c>
-      <c r="I78" s="5" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>p121</t>
         </is>
       </c>
-      <c r="J78" s="5" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/nsh_Avg_Mort_20260729_204519</t>
         </is>
       </c>
-      <c r="K78" s="4" t="n"/>
-    </row>
-    <row r="79" ht="30" customHeight="1">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>nyc_ers</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>New York City (NY) ERS</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>Age_Serv_Wage</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>Active members: average salary by age x years of service</t>
         </is>
       </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
         <is>
           <t>NY_NYC-ERS_AV_2020_76.pdf</t>
         </is>
       </c>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t xml:space="preserve">p108 Detailed Active Membership and Salaries ; p108 Detailed Active Membership and Salaries </t>
         </is>
       </c>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>p108</t>
         </is>
       </c>
-      <c r="J79" s="5" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/nyc_ers_Age_Serv_Wage_20260729_215252</t>
         </is>
       </c>
-      <c r="K79" s="4" t="n"/>
-    </row>
-    <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>nyc_ers</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>New York City (NY) ERS</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>Retirement</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>Retirees: count and average benefit by age band</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G80" s="4" t="inlineStr">
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
         <is>
           <t>NY_NYC-ERS_AV_2020_76.pdf</t>
         </is>
       </c>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>p121 Distribution of Pension Benefits by Caus</t>
         </is>
       </c>
-      <c r="I80" s="5" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>p121</t>
         </is>
       </c>
-      <c r="J80" s="5" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/nyc_ers_Retirement_20260729_222216</t>
         </is>
       </c>
-      <c r="K80" s="4" t="n"/>
-    </row>
-    <row r="81" ht="30" customHeight="1">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>nyc_ers</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>New York City (NY) ERS</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>Sep_Rate</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>Termination/withdrawal rates by age x service</t>
         </is>
       </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="inlineStr">
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t>NY_NYC-ERS_AV_2020_76.pdf</t>
         </is>
       </c>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>p67 Active Termination Rates</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>p75  (the model cited p67 - it used the PRINTED page number; the table is on p75 of the PDF)</t>
         </is>
       </c>
-      <c r="J81" s="5" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/nyc_ers_Sep_Rate_20260729_215802</t>
         </is>
       </c>
-      <c r="K81" s="4" t="n"/>
-    </row>
-    <row r="82" ht="30" customHeight="1">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>phi</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Philadelphia (PA) Municipal</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G82" s="4" t="inlineStr">
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
         <is>
           <t>PA_PHILADELPHIACITY-MPERS_AV_2019_152.pdf</t>
         </is>
       </c>
-      <c r="H82" s="5" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>p78 Distribution of Active Participants (Exc</t>
         </is>
       </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>p78</t>
         </is>
       </c>
-      <c r="J82" s="5" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/phi_Age_Serv_Num_20260729_231022</t>
         </is>
       </c>
-      <c r="K82" s="4" t="n"/>
-    </row>
-    <row r="83" ht="30" customHeight="1">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>phi</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Philadelphia (PA) Municipal</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>Age_Serv_Wage</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>Active members: average salary by age x years of service</t>
         </is>
       </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G83" s="4" t="inlineStr">
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
         <is>
           <t>PA_PHILADELPHIACITY-MPERS_AV_2019_152.pdf</t>
         </is>
       </c>
-      <c r="H83" s="5" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>p78 Distribution of Active Participants (Exc; p78 Distribution of Active Participants (Exc</t>
         </is>
       </c>
-      <c r="I83" s="5" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>p78</t>
         </is>
       </c>
-      <c r="J83" s="5" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/phi_Age_Serv_Wage_20260729_231054</t>
         </is>
       </c>
-      <c r="K83" s="4" t="n"/>
-    </row>
-    <row r="84" ht="30" customHeight="1">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>phi</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Philadelphia (PA) Municipal</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>Retirement</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>Retirees: count and average benefit by age band</t>
         </is>
       </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G84" s="4" t="inlineStr">
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
         <is>
           <t>PA_PHILADELPHIACITY-MPERS_AV_2019_152.pdf</t>
         </is>
       </c>
-      <c r="H84" s="5" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>p87 Table A-26 Age Distribution of Retired M</t>
         </is>
       </c>
-      <c r="I84" s="5" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>p90  (the model cited p87 - it used the PRINTED page number; the table is on p90 of the PDF)</t>
         </is>
       </c>
-      <c r="J84" s="5" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/phi_Retirement_20260729_232051</t>
         </is>
       </c>
-      <c r="K84" s="4" t="n"/>
-    </row>
-    <row r="85" ht="30" customHeight="1">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>phi</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Philadelphia (PA) Municipal</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>Sep_Rate</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>Termination/withdrawal rates by age x service</t>
         </is>
       </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G85" s="4" t="inlineStr">
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
         <is>
           <t>PA_PHILADELPHIACITY-MPERS_AV_2019_152.pdf</t>
         </is>
       </c>
-      <c r="H85" s="5" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>p105 Rates of Termination (Sample Rates)</t>
         </is>
       </c>
-      <c r="I85" s="5" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>p117  (only some values located automatically - check carefully)</t>
         </is>
       </c>
-      <c r="J85" s="5" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/phi_Sep_Rate_20260729_231156</t>
         </is>
       </c>
-      <c r="K85" s="4" t="n"/>
-    </row>
-    <row r="86" ht="30" customHeight="1">
-      <c r="A86" s="4" t="inlineStr">
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B86" s="4" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>phx</t>
         </is>
       </c>
-      <c r="C86" s="4" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Phoenix (AZ) ERS</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G86" s="4" t="inlineStr">
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
         <is>
           <t>AZ_PHOENIXCITY-COPERS_AV_2019_94.pdf</t>
         </is>
       </c>
-      <c r="H86" s="5" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t xml:space="preserve">p38 Exhibit F.3 Active Member Counts by Age </t>
         </is>
       </c>
-      <c r="I86" s="5" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>p38</t>
         </is>
       </c>
-      <c r="J86" s="5" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/phx_Age_Serv_Num_20260729_232111</t>
         </is>
       </c>
-      <c r="K86" s="4" t="n"/>
-    </row>
-    <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>phx</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Phoenix (AZ) ERS</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>Age_Serv_Wage</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>Active members: average salary by age x years of service</t>
         </is>
       </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G87" s="4" t="inlineStr">
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>AZ_PHOENIXCITY-COPERS_AV_2019_94.pdf</t>
         </is>
       </c>
-      <c r="H87" s="5" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>p39 Active Member Average Salary by Age and ; p38 Active Member Counts by Age and Service</t>
         </is>
       </c>
-      <c r="I87" s="5" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>p39</t>
         </is>
       </c>
-      <c r="J87" s="5" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/phx_Age_Serv_Wage_20260729_232127</t>
         </is>
       </c>
-      <c r="K87" s="4" t="n"/>
-    </row>
-    <row r="88" ht="30" customHeight="1">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B88" s="4" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>phx</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Phoenix (AZ) ERS</t>
         </is>
       </c>
-      <c r="D88" s="4" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>Avg_Mort</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>Mortality (death) probability by age</t>
         </is>
       </c>
-      <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G88" s="4" t="inlineStr">
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
         <is>
           <t>AZ_PHOENIXCITY-COPERS_AV_2019_94.pdf</t>
         </is>
       </c>
-      <c r="H88" s="5" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>p48 Sample Probability of Death; p38 Active Member Counts by Age and Service; p41 Summary of Members in Pay Status</t>
         </is>
       </c>
-      <c r="I88" s="5" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>p48</t>
         </is>
       </c>
-      <c r="J88" s="5" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/phx_Avg_Mort_20260729_232223</t>
         </is>
       </c>
-      <c r="K88" s="4" t="n"/>
-    </row>
-    <row r="89" ht="30" customHeight="1">
-      <c r="A89" s="4" t="inlineStr">
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>phx</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Phoenix (AZ) ERS</t>
         </is>
       </c>
-      <c r="D89" s="4" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>Retirement</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>Retirees: count and average benefit by age band</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G89" s="4" t="inlineStr">
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
         <is>
           <t>AZ_PHOENIXCITY-COPERS_AV_2019_94.pdf</t>
         </is>
       </c>
-      <c r="H89" s="5" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>p41 Exhibit F.6 Summary of Members in Pay St</t>
         </is>
       </c>
-      <c r="I89" s="5" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>p41</t>
         </is>
       </c>
-      <c r="J89" s="5" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/phx_Retirement_20260729_232301</t>
         </is>
       </c>
-      <c r="K89" s="4" t="n"/>
-    </row>
-    <row r="90" ht="30" customHeight="1">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>phx</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Phoenix (AZ) ERS</t>
         </is>
       </c>
-      <c r="D90" s="4" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>Sep_Rate</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>Termination/withdrawal rates by age x service</t>
         </is>
       </c>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G90" s="4" t="inlineStr">
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
         <is>
           <t>AZ_PHOENIXCITY-COPERS_AV_2019_94.pdf</t>
         </is>
       </c>
-      <c r="H90" s="5" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>p49 Termination rates (for causes other than</t>
         </is>
       </c>
-      <c r="I90" s="5" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>p49</t>
         </is>
       </c>
-      <c r="J90" s="5" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/phx_Sep_Rate_20260729_232207</t>
         </is>
       </c>
-      <c r="K90" s="4" t="n"/>
-    </row>
-    <row r="91" ht="30" customHeight="1">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>sd</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>San Diego (CA) ERS</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G91" s="4" t="inlineStr">
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
         <is>
           <t>CA_SANDIEGOCITY-SDCERS_AV_2019_144.pdf</t>
         </is>
       </c>
-      <c r="H91" s="5" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>p44 Distribution of Active Members as of Jun</t>
         </is>
       </c>
-      <c r="I91" s="5" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>p44</t>
         </is>
       </c>
-      <c r="J91" s="5" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/sd_Age_Serv_Num_20260729_232320</t>
         </is>
       </c>
-      <c r="K91" s="4" t="n"/>
-    </row>
-    <row r="92" ht="30" customHeight="1">
-      <c r="A92" s="4" t="inlineStr">
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>sd</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>San Diego (CA) ERS</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>Age_Serv_Wage</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>Active members: average salary by age x years of service</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G92" s="4" t="inlineStr">
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
         <is>
           <t>CA_SANDIEGOCITY-SDCERS_AV_2019_144.pdf</t>
         </is>
       </c>
-      <c r="H92" s="5" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>p44 Distribution of Active Members as of Jun; p44 Distribution of Active Members as of Jun</t>
         </is>
       </c>
-      <c r="I92" s="5" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>p44</t>
         </is>
       </c>
-      <c r="J92" s="5" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/sd_Age_Serv_Wage_20260729_232342</t>
         </is>
       </c>
-      <c r="K92" s="4" t="n"/>
-    </row>
-    <row r="93" ht="30" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>sd</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>San Diego (CA) ERS</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>Retirement</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>Retirees: count and average benefit by age band</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G93" s="4" t="inlineStr">
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
         <is>
           <t>CA_SANDIEGOCITY-SDCERS_AV_2019_144.pdf</t>
         </is>
       </c>
-      <c r="H93" s="5" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>p50 Table A-16 Distribution of Retirees (Inc; p47 Table A-13 Retirees (Includes DROP Parti</t>
         </is>
       </c>
-      <c r="I93" s="5" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>p51  (only some values located automatically - check carefully)</t>
         </is>
       </c>
-      <c r="J93" s="5" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/sd_Retirement_20260729_234822</t>
         </is>
       </c>
-      <c r="K93" s="4" t="n"/>
-    </row>
-    <row r="94" ht="30" customHeight="1">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>sd</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>San Diego (CA) ERS</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>Sep_Rate</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>Termination/withdrawal rates by age x service</t>
         </is>
       </c>
-      <c r="F94" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G94" s="4" t="inlineStr">
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>CA_SANDIEGOCITY-SDCERS_AV_2019_144.pdf</t>
         </is>
       </c>
-      <c r="H94" s="5" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>p53 Rates of Termination</t>
         </is>
       </c>
-      <c r="I94" s="5" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>p41  (only some values located automatically - check carefully)</t>
         </is>
       </c>
-      <c r="J94" s="5" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/sd_Sep_Rate_20260729_234142</t>
         </is>
       </c>
-      <c r="K94" s="4" t="n"/>
-    </row>
-    <row r="95" ht="30" customHeight="1">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>sea</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Seattle (WA) ERS</t>
         </is>
       </c>
-      <c r="D95" s="4" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>Avg_Mort</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>Mortality (death) probability by age</t>
         </is>
       </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G95" s="4" t="inlineStr">
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>WA_SEATTLECITY-ERS_AV_2019_156.pdf</t>
         </is>
       </c>
-      <c r="H95" s="5" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>p50 Mortality – Plans 1 and 2; p63 Distribution of Employees and Salaries a; p60 Members Receiving Service Retirement Ben</t>
         </is>
       </c>
-      <c r="I95" s="5" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>p50</t>
         </is>
       </c>
-      <c r="J95" s="5" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/sea_Avg_Mort_20260730_004543</t>
         </is>
       </c>
-      <c r="K95" s="4" t="n"/>
-    </row>
-    <row r="96" ht="30" customHeight="1">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>sea</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Seattle (WA) ERS</t>
         </is>
       </c>
-      <c r="D96" s="4" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>Retirement</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>Retirees: count and average benefit by age band</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G96" s="4" t="inlineStr">
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
         <is>
           <t>WA_SEATTLECITY-ERS_AV_2019_156.pdf</t>
         </is>
       </c>
-      <c r="H96" s="5" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t xml:space="preserve">p60 Members Receiving Service Retirement Ben; p61 Members Receiving Disability Retirement ; p62 Survivors Receiving Retirement Benefits </t>
         </is>
       </c>
-      <c r="I96" s="5" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>p60</t>
         </is>
       </c>
-      <c r="J96" s="5" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/sea_Retirement_20260730_004625</t>
         </is>
       </c>
-      <c r="K96" s="4" t="n"/>
-    </row>
-    <row r="97" ht="30" customHeight="1">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>sea</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>Seattle (WA) ERS</t>
         </is>
       </c>
-      <c r="D97" s="4" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>Sep_Rate</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>Termination/withdrawal rates by age x service</t>
         </is>
       </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G97" s="4" t="inlineStr">
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
         <is>
           <t>WA_SEATTLECITY-ERS_AV_2019_156.pdf</t>
         </is>
       </c>
-      <c r="H97" s="5" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>p51 Other Terminations of Employment Among M</t>
         </is>
       </c>
-      <c r="I97" s="5" t="n"/>
-      <c r="J97" s="5" t="inlineStr">
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/sea_Sep_Rate_20260730_004436</t>
         </is>
       </c>
-      <c r="K97" s="4" t="n"/>
-    </row>
-    <row r="98" ht="30" customHeight="1">
-      <c r="A98" s="4" t="inlineStr">
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B98" s="4" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>sf</t>
         </is>
       </c>
-      <c r="C98" s="4" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>San Francisco (CA) ERS</t>
         </is>
       </c>
-      <c r="D98" s="4" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>Age_Serv_Num</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>Active members: headcount by age x years of service</t>
         </is>
       </c>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G98" s="4" t="inlineStr">
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
         <is>
           <t>CA_SANFRANCITYCOUNTY-SFERS_AV_2019_98.pdf</t>
         </is>
       </c>
-      <c r="H98" s="5" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>p53 Distribution of Active Members as of Jul</t>
         </is>
       </c>
-      <c r="I98" s="5" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>p53</t>
         </is>
       </c>
-      <c r="J98" s="5" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/sf_Age_Serv_Num_20260730_004731</t>
         </is>
       </c>
-      <c r="K98" s="4" t="n"/>
-    </row>
-    <row r="99" ht="30" customHeight="1">
-      <c r="A99" s="4" t="inlineStr">
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>sf</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>San Francisco (CA) ERS</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>Age_Serv_Wage</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>Active members: average salary by age x years of service</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G99" s="4" t="inlineStr">
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
         <is>
           <t>CA_SANFRANCITYCOUNTY-SFERS_AV_2019_98.pdf</t>
         </is>
       </c>
-      <c r="H99" s="5" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>p53 Distribution of Active Members as of Jul; p53 Distribution of Active Members as of Jul</t>
         </is>
       </c>
-      <c r="I99" s="5" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>p53</t>
         </is>
       </c>
-      <c r="J99" s="5" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/sf_Age_Serv_Wage_20260730_004757</t>
         </is>
       </c>
-      <c r="K99" s="4" t="n"/>
-    </row>
-    <row r="100" ht="30" customHeight="1">
-      <c r="A100" s="4" t="inlineStr">
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>sf</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>San Francisco (CA) ERS</t>
         </is>
       </c>
-      <c r="D100" s="4" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>Avg_Mort</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>Mortality (death) probability by age</t>
         </is>
       </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G100" s="4" t="inlineStr">
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
         <is>
           <t>CA_SANFRANCITYCOUNTY-SFERS_AV_2019_98.pdf</t>
         </is>
       </c>
-      <c r="H100" s="5" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>p72 Base Rates of Mortality for Healthy Live; p53 Distribution of Active Members as of Jul; p57 Distribution of Retirees, Disabled Membe</t>
         </is>
       </c>
-      <c r="I100" s="5" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>p72</t>
         </is>
       </c>
-      <c r="J100" s="5" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/sf_Avg_Mort_20260730_005836</t>
         </is>
       </c>
-      <c r="K100" s="4" t="n"/>
-    </row>
-    <row r="101" ht="30" customHeight="1">
-      <c r="A101" s="4" t="inlineStr">
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>3-LOW</t>
         </is>
       </c>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>sf</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>San Francisco (CA) ERS</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>Sep_Rate</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>Termination/withdrawal rates by age x service</t>
         </is>
       </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>no automated check complained - spot-check a few cells</t>
-        </is>
-      </c>
-      <c r="G101" s="4" t="inlineStr">
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>no automated check complained - spot-check a few cells</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
         <is>
           <t>CA_SANFRANCITYCOUNTY-SFERS_AV_2019_98.pdf</t>
         </is>
       </c>
-      <c r="H101" s="5" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>p68 Misc. Rates of Termination by Age and Se</t>
         </is>
       </c>
-      <c r="I101" s="5" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t>p75  (the model cited p68 - it used the PRINTED page number; the table is on p75 of the PDF)</t>
         </is>
       </c>
-      <c r="J101" s="5" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>Data Extraction/runs/_batch_round3/sf_Sep_Rate_20260730_005748</t>
         </is>
       </c>
-      <c r="K101" s="4" t="n"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="K2:K101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick one of the six options." promptTitle="What did you find?" prompt="OK = matches the PDF. Wrong numbers = a digit/cell is misread. Wrong method = numbers right, calculation wrong. Image = the table is a picture, unreadable. Not in PDF = the plan doesn't publish it. Question = needs a methodology decision (don't decide it)." type="list">
-      <formula1>"OK,Wrong numbers,Wrong method,Image,Not in PDF,Question"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K2:K101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Is the extraction correct?" prompt="Correct = matches the PDF. Wrong numbers = a value is misread. Wrong table = it used the wrong exhibit. Wrong method = values right, calculation wrong. Image = table is a picture. Not in PDF = not published. Question = needs a methodology decision (don't decide it)." type="list">
+  <autoFilter ref="A1:M101"/>
+  <dataValidations count="1">
+    <dataValidation sqref="K2:K101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick one" error="Choose one of the seven options." promptTitle="Is the extraction correct?" prompt="Correct = matches the PDF. Wrong numbers = a value misread. Wrong table = wrong exhibit used. Wrong method = values right, calculation wrong. Image = table is a picture. Not in PDF = not published. Question = needs a methodology decision (don't decide it)." type="list">
       <formula1>"Correct,Wrong numbers,Wrong table,Wrong method,Image,Not in PDF,Question"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -6615,13 +6292,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1574432F-9C01-49F5-A9EC-1A0BDF7B1DF9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B01C19-01E0-41D2-813E-A57DEA321648}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29FA5E61-25A3-472A-B88A-78B8E1B91EDF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78FF1695-F79E-4EA2-852A-7A2340419314}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8A1D54A-0D31-4560-8DFD-B67CA64F76FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80962F69-1C0B-48F6-9145-FB0359D8CB14}"/>
 </file>
--- a/Data Extraction/verification/model_output_verif_worklist.xlsx
+++ b/Data Extraction/verification/model_output_verif_worklist.xlsx
@@ -9,9 +9,7 @@
   <sheets>
     <sheet name="verification" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'verification'!$A$1:$M$101</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -31,17 +29,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDE5F0"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -56,14 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,7 +435,7 @@
     <col width="26" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
@@ -566,7 +554,7 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -621,7 +609,7 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -676,7 +664,7 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -731,7 +719,7 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -786,7 +774,7 @@
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -841,7 +829,7 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -896,7 +884,7 @@
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -951,7 +939,7 @@
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1006,7 +994,7 @@
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1061,7 +1049,7 @@
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1116,7 +1104,7 @@
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1171,7 +1159,7 @@
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1226,7 +1214,7 @@
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1281,7 +1269,7 @@
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1336,7 +1324,7 @@
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1391,7 +1379,7 @@
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1446,7 +1434,7 @@
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1501,7 +1489,7 @@
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1556,7 +1544,7 @@
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1611,7 +1599,7 @@
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1666,7 +1654,7 @@
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1721,7 +1709,7 @@
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1776,7 +1764,7 @@
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1831,7 +1819,7 @@
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1882,7 +1870,7 @@
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1937,7 +1925,7 @@
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1992,7 +1980,7 @@
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -2047,7 +2035,7 @@
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -2098,7 +2086,7 @@
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -2153,7 +2141,7 @@
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -2208,7 +2196,7 @@
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -2263,7 +2251,7 @@
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
@@ -2318,7 +2306,7 @@
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -2373,7 +2361,7 @@
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -2428,7 +2416,7 @@
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -2483,7 +2471,7 @@
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -2538,7 +2526,7 @@
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -2593,7 +2581,7 @@
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
@@ -2648,7 +2636,7 @@
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
@@ -2703,7 +2691,7 @@
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -2758,7 +2746,7 @@
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -2813,7 +2801,7 @@
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -2868,7 +2856,7 @@
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -2923,7 +2911,7 @@
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -2978,7 +2966,7 @@
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -3033,7 +3021,7 @@
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -3088,7 +3076,7 @@
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -3143,7 +3131,7 @@
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -3198,7 +3186,7 @@
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -3249,7 +3237,7 @@
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" s="2" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -3304,7 +3292,7 @@
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -3359,7 +3347,7 @@
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" s="2" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -3414,7 +3402,7 @@
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -3469,7 +3457,7 @@
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" s="2" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -3524,7 +3512,7 @@
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -3579,7 +3567,7 @@
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" s="2" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -3634,7 +3622,7 @@
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -3689,7 +3677,7 @@
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" s="2" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -3744,7 +3732,7 @@
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -3799,7 +3787,7 @@
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" s="2" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
@@ -3854,7 +3842,7 @@
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" s="2" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -3909,7 +3897,7 @@
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" s="2" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
@@ -3964,7 +3952,7 @@
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" s="2" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -4019,7 +4007,7 @@
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" s="2" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
@@ -4074,7 +4062,7 @@
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" s="2" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
     </row>
     <row r="67">
@@ -4129,7 +4117,7 @@
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" s="2" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
     </row>
     <row r="68">
@@ -4184,7 +4172,7 @@
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" s="2" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
     </row>
     <row r="69">
@@ -4239,7 +4227,7 @@
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" s="2" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
     </row>
     <row r="70">
@@ -4294,7 +4282,7 @@
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
@@ -4349,7 +4337,7 @@
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" s="2" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
@@ -4404,7 +4392,7 @@
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" s="2" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
     </row>
     <row r="73">
@@ -4459,7 +4447,7 @@
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" s="2" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
@@ -4514,7 +4502,7 @@
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
@@ -4569,7 +4557,7 @@
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" s="2" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
     </row>
     <row r="76">
@@ -4624,7 +4612,7 @@
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
@@ -4679,7 +4667,7 @@
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" s="2" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
     </row>
     <row r="78">
@@ -4734,7 +4722,7 @@
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" s="2" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
     </row>
     <row r="79">
@@ -4789,7 +4777,7 @@
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" s="2" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
     </row>
     <row r="80">
@@ -4844,7 +4832,7 @@
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
     </row>
     <row r="81">
@@ -4899,7 +4887,7 @@
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" s="2" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
     </row>
     <row r="82">
@@ -4954,7 +4942,7 @@
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" s="2" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
     </row>
     <row r="83">
@@ -5009,7 +4997,7 @@
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" s="2" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
     </row>
     <row r="84">
@@ -5064,7 +5052,7 @@
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" s="2" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
@@ -5119,7 +5107,7 @@
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" s="2" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
     </row>
     <row r="86">
@@ -5174,7 +5162,7 @@
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" s="2" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
     </row>
     <row r="87">
@@ -5229,7 +5217,7 @@
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" s="2" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
     </row>
     <row r="88">
@@ -5284,7 +5272,7 @@
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
     </row>
     <row r="89">
@@ -5339,7 +5327,7 @@
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" s="2" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
@@ -5394,7 +5382,7 @@
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" s="2" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
     </row>
     <row r="91">
@@ -5449,7 +5437,7 @@
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" s="2" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
     </row>
     <row r="92">
@@ -5504,7 +5492,7 @@
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" s="2" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
     </row>
     <row r="93">
@@ -5559,7 +5547,7 @@
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" s="2" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
     </row>
     <row r="94">
@@ -5614,7 +5602,7 @@
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" s="2" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
     </row>
     <row r="95">
@@ -5669,7 +5657,7 @@
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" s="2" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
     </row>
     <row r="96">
@@ -5724,7 +5712,7 @@
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
-      <c r="L96" s="2" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
     </row>
     <row r="97">
@@ -5775,7 +5763,7 @@
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" s="2" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
     </row>
     <row r="98">
@@ -5830,7 +5818,7 @@
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" s="2" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
     </row>
     <row r="99">
@@ -5885,7 +5873,7 @@
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" s="2" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
@@ -5940,7 +5928,7 @@
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
-      <c r="L100" s="2" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
@@ -5995,16 +5983,10 @@
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" s="2" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M101"/>
-  <dataValidations count="1">
-    <dataValidation sqref="K2:K101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick one" error="Choose one of the seven options." promptTitle="Is the extraction correct?" prompt="Correct = matches the PDF. Wrong numbers = a value misread. Wrong table = wrong exhibit used. Wrong method = values right, calculation wrong. Image = table is a picture. Not in PDF = not published. Question = needs a methodology decision (don't decide it)." type="list">
-      <formula1>"Correct,Wrong numbers,Wrong table,Wrong method,Image,Not in PDF,Question"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6292,13 +6274,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B01C19-01E0-41D2-813E-A57DEA321648}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A03A84B-0B0C-4A2E-8492-149A72768352}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78FF1695-F79E-4EA2-852A-7A2340419314}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20630461-4458-44BE-AA4B-54A5C230FEF0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80962F69-1C0B-48F6-9145-FB0359D8CB14}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1011D01F-DA10-4ACA-8DAC-3637BBB2A22F}"/>
 </file>